--- a/.work/export-verified.xlsx
+++ b/.work/export-verified.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="送样记录" sheetId="1" r:id="R46c8bde3b4fa4795"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="归还明细" sheetId="2" r:id="Rbcac4a04fb3b4e52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="送样记录" sheetId="1" r:id="R3731ac5ffd07433b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="归还明细" sheetId="2" r:id="R40f78b9e4b8e457a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -356,7 +356,7 @@
       </x:c>
       <x:c r="B2" s="1" t="inlineStr">
         <x:is>
-          <x:t>2026-09-17 14:05</x:t>
+          <x:t>2026-09-20 14:37</x:t>
         </x:is>
       </x:c>
       <x:c r="C2" s="1"/>
@@ -546,7 +546,7 @@
       </x:c>
       <x:c r="M5" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">借出中</x:t>
+          <x:t xml:space="preserve">即将到期</x:t>
         </x:is>
       </x:c>
       <x:c r="N5" s="8" t="inlineStr">
@@ -1282,7 +1282,7 @@
     <x:row r="13">
       <x:c r="A13" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">RD-16B618F0</x:t>
+          <x:t xml:space="preserve">RD-B54494C8</x:t>
         </x:is>
       </x:c>
       <x:c r="B13" s="8" t="inlineStr">
@@ -1318,7 +1318,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J13" s="10" t="n">
-        <x:v>46282</x:v>
+        <x:v>46285</x:v>
       </x:c>
       <x:c r="K13" s="10"/>
       <x:c r="L13" s="10"/>
@@ -1366,6 +1366,8 @@
     <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -1380,6 +1382,8 @@
       <x:c r="G1" s="3"/>
       <x:c r="H1" s="3"/>
       <x:c r="I1" s="3"/>
+      <x:c r="J1" s="3"/>
+      <x:c r="K1" s="3"/>
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="1" t="str">
@@ -1387,7 +1391,7 @@
       </x:c>
       <x:c r="B2" s="1" t="inlineStr">
         <x:is>
-          <x:t>2026-09-17 14:05</x:t>
+          <x:t>2026-09-20 14:37</x:t>
         </x:is>
       </x:c>
       <x:c r="C2" s="1"/>
@@ -1397,6 +1401,8 @@
       <x:c r="G2" s="1"/>
       <x:c r="H2" s="1"/>
       <x:c r="I2" s="1"/>
+      <x:c r="J2" s="1"/>
+      <x:c r="K2" s="1"/>
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="1"/>
@@ -1408,6 +1414,8 @@
       <x:c r="G3" s="1"/>
       <x:c r="H3" s="1"/>
       <x:c r="I3" s="1"/>
+      <x:c r="J3" s="1"/>
+      <x:c r="K3" s="1"/>
     </x:row>
     <x:row r="4" ht="28" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -1437,6 +1445,12 @@
       <x:c r="I4" s="6" t="str">
         <x:v>归还备注</x:v>
       </x:c>
+      <x:c r="J4" s="6" t="str">
+        <x:v>客户是否提供测试报告</x:v>
+      </x:c>
+      <x:c r="K4" s="6" t="str">
+        <x:v>测试报告文件名</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="8" t="inlineStr">
@@ -1476,9 +1490,15 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="I5" s="8"/>
+      <x:c r="J5" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">未登记</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K5" s="8"/>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A4:I5"/>
+  <x:autoFilter ref="A4:K5"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/.work/export-verified.xlsx
+++ b/.work/export-verified.xlsx
@@ -356,7 +356,7 @@
       </x:c>
       <x:c r="B2" s="1" t="inlineStr">
         <x:is>
-          <x:t>2026-09-20 14:37</x:t>
+          <x:t>2026-09-20 17:06</x:t>
         </x:is>
       </x:c>
       <x:c r="C2" s="1"/>
@@ -1282,7 +1282,7 @@
     <x:row r="13">
       <x:c r="A13" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">RD-B54494C8</x:t>
+          <x:t xml:space="preserve">RD-59E1F1F8</x:t>
         </x:is>
       </x:c>
       <x:c r="B13" s="8" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </x:c>
       <x:c r="B2" s="1" t="inlineStr">
         <x:is>
-          <x:t>2026-09-20 14:37</x:t>
+          <x:t>2026-09-20 17:06</x:t>
         </x:is>
       </x:c>
       <x:c r="C2" s="1"/>
